--- a/04_DESIGN_TABLES/DesignTable_6400_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6400_SW2.xlsx
@@ -3392,7 +3392,7 @@
         <v>0.05556</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.391</v>
+        <v>0.3</v>
       </c>
       <c r="AD19" t="n">
         <v>0.631</v>
@@ -3435,12 +3435,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED); D4@BORE_A: OMi WebsitePartsInfo2026.xlsx Items!X1639 = 0.391 (table had 0.3) [user 2026-10-18 A19] | MODEL: End A male SAE ORB end of the second dash and End B male 37deg JIC end of the first dash from the END LIBRARIES (ORB: thread major / length, groove dia / width of the 6401 / 6405 / 6410 review rows + the 6408 -02 / -14 / -32 rows, groove width 0.125 at -14 / -32 measured on the Brennan 6400-14-14-O / 6400-32-32-O STEPs (A18 2026-10-18); JIC: MS33656J chain per dash, 2403 table, VERIFIED vs Brennan; no tip chamfers) - equal to the ORB / JIC columns of the 6400 review table (cross-checked per row); D1 overall / hex / bores D4 (ORB side) and D3 (JIC side): review table (Air-Way; OMi = Air-Way on the A23 rows); hex over the whole length between the two ends; bore step D4 / D3 at the hex mid-plane (ASSUMPTION - the rule of the hand-made 6400 table, as 2403); hex end chamfers NOT modelled; rebuilt by the generator 2026-10-18 (user A6), replaces the hand-made 6400 master</t>
+          <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED); D4@BORE_A: OMi WebsitePartsInfo2026.xlsx Items!X1639 = 0.391 (table had 0.3) [user 2026-10-18 A19]; D4@BORE_A: Air-Way 0.3 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.391) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: End A male SAE ORB end of the second dash and End B male 37deg JIC end of the first dash from the END LIBRARIES (ORB: thread major / length, groove dia / width of the 6401 / 6405 / 6410 review rows + the 6408 -02 / -14 / -32 rows, groove width 0.125 at -14 / -32 measured on the Brennan 6400-14-14-O / 6400-32-32-O STEPs (A18 2026-10-18); JIC: MS33656J chain per dash, 2403 table, VERIFIED vs Brennan; no tip chamfers) - equal to the ORB / JIC columns of the 6400 review table (cross-checked per row); D1 overall / hex / bores D4 (ORB side) and D3 (JIC side): review table (Air-Way; OMi = Air-Way on the A23 rows); hex over the whole length between the two ends; bore step D4 / D3 at the hex mid-plane (ASSUMPTION - the rule of the hand-made 6400 table, as 2403); hex end chamfers NOT modelled; rebuilt by the generator 2026-10-18 (user A6), replaces the hand-made 6400 master</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 1 certain): D4@BORE_A 0.3 -&gt; OMi 0.391 (Items!X1639, M158)</t>
+          <t>A19 (user 2026-10-18, group 1 certain): D4@BORE_A 0.3 -&gt; OMi 0.391 (Items!X1639, M158) | 2026-10-20 Air-Way first: D4@BORE_A OMi/Brennan 0.391 -&gt; Air-Way 0.3</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="C22" t="n">
         <v>0.86603</v>
@@ -3869,13 +3869,13 @@
         <v>0.84</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.864</v>
+        <v>0.859</v>
       </c>
       <c r="AE22" t="n">
         <v>0.3</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.826</v>
+        <v>0.821</v>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
@@ -3909,12 +3909,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>JIC: VERIFIED (MS33656J=Brennan, confirmed on 6400 models); ORB thd: MS51527 J2 transfer (ASSUMED); GRVW: measured (ASSUMED); D1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1642 = 1.69 (table had 1.68) [user 2026-10-18 A19] | MODEL: End A male SAE ORB end of the second dash and End B male 37deg JIC end of the first dash from the END LIBRARIES (ORB: thread major / length, groove dia / width of the 6401 / 6405 / 6410 review rows + the 6408 -02 / -14 / -32 rows, groove width 0.125 at -14 / -32 measured on the Brennan 6400-14-14-O / 6400-32-32-O STEPs (A18 2026-10-18); JIC: MS33656J chain per dash, 2403 table, VERIFIED vs Brennan; no tip chamfers) - equal to the ORB / JIC columns of the 6400 review table (cross-checked per row); D1 overall / hex / bores D4 (ORB side) and D3 (JIC side): review table (Air-Way; OMi = Air-Way on the A23 rows); hex over the whole length between the two ends; bore step D4 / D3 at the hex mid-plane (ASSUMPTION - the rule of the hand-made 6400 table, as 2403); hex end chamfers NOT modelled; rebuilt by the generator 2026-10-18 (user A6), replaces the hand-made 6400 master</t>
+          <t>JIC: VERIFIED (MS33656J=Brennan, confirmed on 6400 models); ORB thd: MS51527 J2 transfer (ASSUMED); GRVW: measured (ASSUMED); D1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1642 = 1.69 (table had 1.68) [user 2026-10-18 A19]; D1@DRIVE: Air-Way 1.68 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.69) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: End A male SAE ORB end of the second dash and End B male 37deg JIC end of the first dash from the END LIBRARIES (ORB: thread major / length, groove dia / width of the 6401 / 6405 / 6410 review rows + the 6408 -02 / -14 / -32 rows, groove width 0.125 at -14 / -32 measured on the Brennan 6400-14-14-O / 6400-32-32-O STEPs (A18 2026-10-18); JIC: MS33656J chain per dash, 2403 table, VERIFIED vs Brennan; no tip chamfers) - equal to the ORB / JIC columns of the 6400 review table (cross-checked per row); D1 overall / hex / bores D4 (ORB side) and D3 (JIC side): review table (Air-Way; OMi = Air-Way on the A23 rows); hex over the whole length between the two ends; bore step D4 / D3 at the hex mid-plane (ASSUMPTION - the rule of the hand-made 6400 table, as 2403); hex end chamfers NOT modelled; rebuilt by the generator 2026-10-18 (user A6), replaces the hand-made 6400 master</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>ORB_GRVW measured from Brennan 6400 STEP (ASSUMED, single source; method validated on -4/-12 pub values) | A19 (user 2026-10-18, group 1 certain): D1@DRIVE 1.68 -&gt; OMi 1.69 (Items!L1642, M155)</t>
+          <t>ORB_GRVW measured from Brennan 6400 STEP (ASSUMED, single source; method validated on -4/-12 pub values) | A19 (user 2026-10-18, group 1 certain): D1@DRIVE 1.68 -&gt; OMi 1.69 (Items!L1642, M155) | 2026-10-20 Air-Way first: D1@DRIVE OMi/Brennan 1.69 -&gt; Air-Way 1.68</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -3946,10 +3946,10 @@
         <v>1.49</v>
       </c>
       <c r="C23" t="n">
-        <v>0.50518</v>
+        <v>0.46765</v>
       </c>
       <c r="D23" t="n">
-        <v>0.875</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E23" t="n">
         <v>0.21875</v>
@@ -4067,12 +4067,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED); HEXB@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1643 = 0.875 (table had 0.8125) [user 2026-10-18 A19] | MODEL: End A male SAE ORB end of the second dash and End B male 37deg JIC end of the first dash from the END LIBRARIES (ORB: thread major / length, groove dia / width of the 6401 / 6405 / 6410 review rows + the 6408 -02 / -14 / -32 rows, groove width 0.125 at -14 / -32 measured on the Brennan 6400-14-14-O / 6400-32-32-O STEPs (A18 2026-10-18); JIC: MS33656J chain per dash, 2403 table, VERIFIED vs Brennan; no tip chamfers) - equal to the ORB / JIC columns of the 6400 review table (cross-checked per row); D1 overall / hex / bores D4 (ORB side) and D3 (JIC side): review table (Air-Way; OMi = Air-Way on the A23 rows); hex over the whole length between the two ends; bore step D4 / D3 at the hex mid-plane (ASSUMPTION - the rule of the hand-made 6400 table, as 2403); hex end chamfers NOT modelled; rebuilt by the generator 2026-10-18 (user A6), replaces the hand-made 6400 master</t>
+          <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED); HEXB@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1643 = 0.875 (table had 0.8125) [user 2026-10-18 A19]; HEXB@HEX: Air-Way 0.81 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.875) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: End A male SAE ORB end of the second dash and End B male 37deg JIC end of the first dash from the END LIBRARIES (ORB: thread major / length, groove dia / width of the 6401 / 6405 / 6410 review rows + the 6408 -02 / -14 / -32 rows, groove width 0.125 at -14 / -32 measured on the Brennan 6400-14-14-O / 6400-32-32-O STEPs (A18 2026-10-18); JIC: MS33656J chain per dash, 2403 table, VERIFIED vs Brennan; no tip chamfers) - equal to the ORB / JIC columns of the 6400 review table (cross-checked per row); D1 overall / hex / bores D4 (ORB side) and D3 (JIC side): review table (Air-Way; OMi = Air-Way on the A23 rows); hex over the whole length between the two ends; bore step D4 / D3 at the hex mid-plane (ASSUMPTION - the rule of the hand-made 6400 table, as 2403); hex end chamfers NOT modelled; rebuilt by the generator 2026-10-18 (user A6), replaces the hand-made 6400 master</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 1 certain): HEXB@HEX 0.8125 -&gt; OMi 0.875 (Items!R1643, M156)</t>
+          <t>A19 (user 2026-10-18, group 1 certain): HEXB@HEX 0.8125 -&gt; OMi 0.875 (Items!R1643, M156) | 2026-10-20 Air-Way first: HEXB@HEX OMi/Brennan 0.875 -&gt; Air-Way 0.81</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -4894,10 +4894,10 @@
         <v>1.71</v>
       </c>
       <c r="C29" t="n">
-        <v>0.57735</v>
+        <v>0.54271</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E29" t="n">
         <v>0.28125</v>
@@ -5015,12 +5015,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED); HEXB@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1651 = 1.000 (table had 0.9375) [user 2026-10-18 A19] | MODEL: End A male SAE ORB end of the second dash and End B male 37deg JIC end of the first dash from the END LIBRARIES (ORB: thread major / length, groove dia / width of the 6401 / 6405 / 6410 review rows + the 6408 -02 / -14 / -32 rows, groove width 0.125 at -14 / -32 measured on the Brennan 6400-14-14-O / 6400-32-32-O STEPs (A18 2026-10-18); JIC: MS33656J chain per dash, 2403 table, VERIFIED vs Brennan; no tip chamfers) - equal to the ORB / JIC columns of the 6400 review table (cross-checked per row); D1 overall / hex / bores D4 (ORB side) and D3 (JIC side): review table (Air-Way; OMi = Air-Way on the A23 rows); hex over the whole length between the two ends; bore step D4 / D3 at the hex mid-plane (ASSUMPTION - the rule of the hand-made 6400 table, as 2403); hex end chamfers NOT modelled; rebuilt by the generator 2026-10-18 (user A6), replaces the hand-made 6400 master</t>
+          <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED); HEXB@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1651 = 1.000 (table had 0.9375) [user 2026-10-18 A19]; HEXB@HEX: Air-Way 0.94 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: End A male SAE ORB end of the second dash and End B male 37deg JIC end of the first dash from the END LIBRARIES (ORB: thread major / length, groove dia / width of the 6401 / 6405 / 6410 review rows + the 6408 -02 / -14 / -32 rows, groove width 0.125 at -14 / -32 measured on the Brennan 6400-14-14-O / 6400-32-32-O STEPs (A18 2026-10-18); JIC: MS33656J chain per dash, 2403 table, VERIFIED vs Brennan; no tip chamfers) - equal to the ORB / JIC columns of the 6400 review table (cross-checked per row); D1 overall / hex / bores D4 (ORB side) and D3 (JIC side): review table (Air-Way; OMi = Air-Way on the A23 rows); hex over the whole length between the two ends; bore step D4 / D3 at the hex mid-plane (ASSUMPTION - the rule of the hand-made 6400 table, as 2403); hex end chamfers NOT modelled; rebuilt by the generator 2026-10-18 (user A6), replaces the hand-made 6400 master</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 1 certain): HEXB@HEX 0.9375 -&gt; OMi 1.000 (Items!R1651, M156)</t>
+          <t>A19 (user 2026-10-18, group 1 certain): HEXB@HEX 0.9375 -&gt; OMi 1.000 (Items!R1651, M156) | 2026-10-20 Air-Way first: HEXB@HEX OMi/Brennan 1 -&gt; Air-Way 0.94</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
@@ -5052,10 +5052,10 @@
         <v>1.64</v>
       </c>
       <c r="C30" t="n">
-        <v>0.57735</v>
+        <v>0.54271</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E30" t="n">
         <v>0.375</v>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED); HEXB@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1652 = 1.000 (table had 0.9375) [user 2026-10-18 A19] | MODEL: End A male SAE ORB end of the second dash and End B male 37deg JIC end of the first dash from the END LIBRARIES (ORB: thread major / length, groove dia / width of the 6401 / 6405 / 6410 review rows + the 6408 -02 / -14 / -32 rows, groove width 0.125 at -14 / -32 measured on the Brennan 6400-14-14-O / 6400-32-32-O STEPs (A18 2026-10-18); JIC: MS33656J chain per dash, 2403 table, VERIFIED vs Brennan; no tip chamfers) - equal to the ORB / JIC columns of the 6400 review table (cross-checked per row); D1 overall / hex / bores D4 (ORB side) and D3 (JIC side): review table (Air-Way; OMi = Air-Way on the A23 rows); hex over the whole length between the two ends; bore step D4 / D3 at the hex mid-plane (ASSUMPTION - the rule of the hand-made 6400 table, as 2403); hex end chamfers NOT modelled; rebuilt by the generator 2026-10-18 (user A6), replaces the hand-made 6400 master</t>
+          <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED); HEXB@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1652 = 1.000 (table had 0.9375) [user 2026-10-18 A19]; HEXB@HEX: Air-Way 0.94 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: End A male SAE ORB end of the second dash and End B male 37deg JIC end of the first dash from the END LIBRARIES (ORB: thread major / length, groove dia / width of the 6401 / 6405 / 6410 review rows + the 6408 -02 / -14 / -32 rows, groove width 0.125 at -14 / -32 measured on the Brennan 6400-14-14-O / 6400-32-32-O STEPs (A18 2026-10-18); JIC: MS33656J chain per dash, 2403 table, VERIFIED vs Brennan; no tip chamfers) - equal to the ORB / JIC columns of the 6400 review table (cross-checked per row); D1 overall / hex / bores D4 (ORB side) and D3 (JIC side): review table (Air-Way; OMi = Air-Way on the A23 rows); hex over the whole length between the two ends; bore step D4 / D3 at the hex mid-plane (ASSUMPTION - the rule of the hand-made 6400 table, as 2403); hex end chamfers NOT modelled; rebuilt by the generator 2026-10-18 (user A6), replaces the hand-made 6400 master</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 1 certain): HEXB@HEX 0.9375 -&gt; OMi 1.000 (Items!R1652, M156)</t>
+          <t>A19 (user 2026-10-18, group 1 certain): HEXB@HEX 0.9375 -&gt; OMi 1.000 (Items!R1652, M156) | 2026-10-20 Air-Way first: HEXB@HEX OMi/Brennan 1 -&gt; Air-Way 0.94</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -5441,7 +5441,7 @@
         <v>0.07142999999999999</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.609</v>
+        <v>0.48</v>
       </c>
       <c r="AD32" t="n">
         <v>0.848</v>
@@ -5484,12 +5484,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED); D4@BORE_A: OMi WebsitePartsInfo2026.xlsx Items!X1654 = 0.609 (table had 0.48) [user 2026-10-18 A19] | MODEL: End A male SAE ORB end of the second dash and End B male 37deg JIC end of the first dash from the END LIBRARIES (ORB: thread major / length, groove dia / width of the 6401 / 6405 / 6410 review rows + the 6408 -02 / -14 / -32 rows, groove width 0.125 at -14 / -32 measured on the Brennan 6400-14-14-O / 6400-32-32-O STEPs (A18 2026-10-18); JIC: MS33656J chain per dash, 2403 table, VERIFIED vs Brennan; no tip chamfers) - equal to the ORB / JIC columns of the 6400 review table (cross-checked per row); D1 overall / hex / bores D4 (ORB side) and D3 (JIC side): review table (Air-Way; OMi = Air-Way on the A23 rows); hex over the whole length between the two ends; bore step D4 / D3 at the hex mid-plane (ASSUMPTION - the rule of the hand-made 6400 table, as 2403); hex end chamfers NOT modelled; rebuilt by the generator 2026-10-18 (user A6), replaces the hand-made 6400 master</t>
+          <t>JIC: VERIFIED (MS33656J = Brennan fleet); ORB thd: MS51527 J2 transfer (ASSUMED); D4@BORE_A: OMi WebsitePartsInfo2026.xlsx Items!X1654 = 0.609 (table had 0.48) [user 2026-10-18 A19]; D4@BORE_A: Air-Way 0.48 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.609) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: End A male SAE ORB end of the second dash and End B male 37deg JIC end of the first dash from the END LIBRARIES (ORB: thread major / length, groove dia / width of the 6401 / 6405 / 6410 review rows + the 6408 -02 / -14 / -32 rows, groove width 0.125 at -14 / -32 measured on the Brennan 6400-14-14-O / 6400-32-32-O STEPs (A18 2026-10-18); JIC: MS33656J chain per dash, 2403 table, VERIFIED vs Brennan; no tip chamfers) - equal to the ORB / JIC columns of the 6400 review table (cross-checked per row); D1 overall / hex / bores D4 (ORB side) and D3 (JIC side): review table (Air-Way; OMi = Air-Way on the A23 rows); hex over the whole length between the two ends; bore step D4 / D3 at the hex mid-plane (ASSUMPTION - the rule of the hand-made 6400 table, as 2403); hex end chamfers NOT modelled; rebuilt by the generator 2026-10-18 (user A6), replaces the hand-made 6400 master</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 1 certain): D4@BORE_A 0.48 -&gt; OMi 0.609 (Items!X1654, M158)</t>
+          <t>A19 (user 2026-10-18, group 1 certain): D4@BORE_A 0.48 -&gt; OMi 0.609 (Items!X1654, M158) | 2026-10-20 Air-Way first: D4@BORE_A OMi/Brennan 0.609 -&gt; Air-Way 0.48</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
@@ -8992,10 +8992,10 @@
         <v>2.53</v>
       </c>
       <c r="C55" t="n">
-        <v>1.22687</v>
+        <v>1.1547</v>
       </c>
       <c r="D55" t="n">
-        <v>2.125</v>
+        <v>2</v>
       </c>
       <c r="E55" t="n">
         <v>0.65625</v>
@@ -9113,12 +9113,12 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>JIC: VERIFIED (MS33656J=Brennan, confirmed on 6400 models); ORB thd: MS51527 J2 transfer (ASSUMED); GRVW: measured (ASSUMED); HEXB@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1682 = 2.125 (table had 2) [user 2026-10-18 A19] | MODEL: End A male SAE ORB end of the second dash and End B male 37deg JIC end of the first dash from the END LIBRARIES (ORB: thread major / length, groove dia / width of the 6401 / 6405 / 6410 review rows + the 6408 -02 / -14 / -32 rows, groove width 0.125 at -14 / -32 measured on the Brennan 6400-14-14-O / 6400-32-32-O STEPs (A18 2026-10-18); JIC: MS33656J chain per dash, 2403 table, VERIFIED vs Brennan; no tip chamfers) - equal to the ORB / JIC columns of the 6400 review table (cross-checked per row); D1 overall / hex / bores D4 (ORB side) and D3 (JIC side): review table (Air-Way; OMi = Air-Way on the A23 rows); hex over the whole length between the two ends; bore step D4 / D3 at the hex mid-plane (ASSUMPTION - the rule of the hand-made 6400 table, as 2403); hex end chamfers NOT modelled; rebuilt by the generator 2026-10-18 (user A6), replaces the hand-made 6400 master</t>
+          <t>JIC: VERIFIED (MS33656J=Brennan, confirmed on 6400 models); ORB thd: MS51527 J2 transfer (ASSUMED); GRVW: measured (ASSUMED); HEXB@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1682 = 2.125 (table had 2) [user 2026-10-18 A19]; HEXB@HEX: Air-Way 2 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.125) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: End A male SAE ORB end of the second dash and End B male 37deg JIC end of the first dash from the END LIBRARIES (ORB: thread major / length, groove dia / width of the 6401 / 6405 / 6410 review rows + the 6408 -02 / -14 / -32 rows, groove width 0.125 at -14 / -32 measured on the Brennan 6400-14-14-O / 6400-32-32-O STEPs (A18 2026-10-18); JIC: MS33656J chain per dash, 2403 table, VERIFIED vs Brennan; no tip chamfers) - equal to the ORB / JIC columns of the 6400 review table (cross-checked per row); D1 overall / hex / bores D4 (ORB side) and D3 (JIC side): review table (Air-Way; OMi = Air-Way on the A23 rows); hex over the whole length between the two ends; bore step D4 / D3 at the hex mid-plane (ASSUMPTION - the rule of the hand-made 6400 table, as 2403); hex end chamfers NOT modelled; rebuilt by the generator 2026-10-18 (user A6), replaces the hand-made 6400 master</t>
         </is>
       </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>ORB_GRVW measured from Brennan 6400 STEP (ASSUMED, single source; method validated on -4/-12 pub values) | A19 (user 2026-10-18, group 1 certain): HEXB@HEX 2 -&gt; OMi 2.125 (Items!R1682, M156)</t>
+          <t>ORB_GRVW measured from Brennan 6400 STEP (ASSUMED, single source; method validated on -4/-12 pub values) | A19 (user 2026-10-18, group 1 certain): HEXB@HEX 2 -&gt; OMi 2.125 (Items!R1682, M156) | 2026-10-20 Air-Way first: HEXB@HEX OMi/Brennan 2.125 -&gt; Air-Way 2</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
@@ -9150,10 +9150,10 @@
         <v>2.53</v>
       </c>
       <c r="C56" t="n">
-        <v>1.22687</v>
+        <v>1.1547</v>
       </c>
       <c r="D56" t="n">
-        <v>2.125</v>
+        <v>2</v>
       </c>
       <c r="E56" t="n">
         <v>0.8125</v>
@@ -9271,12 +9271,12 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>JIC: VERIFIED (MS33656J=Brennan, confirmed on 6400 models); ORB thd: MS51527 J2 transfer (ASSUMED); GRVW: measured (ASSUMED); HEXB@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1683 = 2.125 (table had 2) [user 2026-10-18 A19] | MODEL: End A male SAE ORB end of the second dash and End B male 37deg JIC end of the first dash from the END LIBRARIES (ORB: thread major / length, groove dia / width of the 6401 / 6405 / 6410 review rows + the 6408 -02 / -14 / -32 rows, groove width 0.125 at -14 / -32 measured on the Brennan 6400-14-14-O / 6400-32-32-O STEPs (A18 2026-10-18); JIC: MS33656J chain per dash, 2403 table, VERIFIED vs Brennan; no tip chamfers) - equal to the ORB / JIC columns of the 6400 review table (cross-checked per row); D1 overall / hex / bores D4 (ORB side) and D3 (JIC side): review table (Air-Way; OMi = Air-Way on the A23 rows); hex over the whole length between the two ends; bore step D4 / D3 at the hex mid-plane (ASSUMPTION - the rule of the hand-made 6400 table, as 2403); hex end chamfers NOT modelled; rebuilt by the generator 2026-10-18 (user A6), replaces the hand-made 6400 master</t>
+          <t>JIC: VERIFIED (MS33656J=Brennan, confirmed on 6400 models); ORB thd: MS51527 J2 transfer (ASSUMED); GRVW: measured (ASSUMED); HEXB@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1683 = 2.125 (table had 2) [user 2026-10-18 A19]; HEXB@HEX: Air-Way 2 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.125) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: End A male SAE ORB end of the second dash and End B male 37deg JIC end of the first dash from the END LIBRARIES (ORB: thread major / length, groove dia / width of the 6401 / 6405 / 6410 review rows + the 6408 -02 / -14 / -32 rows, groove width 0.125 at -14 / -32 measured on the Brennan 6400-14-14-O / 6400-32-32-O STEPs (A18 2026-10-18); JIC: MS33656J chain per dash, 2403 table, VERIFIED vs Brennan; no tip chamfers) - equal to the ORB / JIC columns of the 6400 review table (cross-checked per row); D1 overall / hex / bores D4 (ORB side) and D3 (JIC side): review table (Air-Way; OMi = Air-Way on the A23 rows); hex over the whole length between the two ends; bore step D4 / D3 at the hex mid-plane (ASSUMPTION - the rule of the hand-made 6400 table, as 2403); hex end chamfers NOT modelled; rebuilt by the generator 2026-10-18 (user A6), replaces the hand-made 6400 master</t>
         </is>
       </c>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>ORB_GRVW measured from Brennan 6400-32-20-O STEP (ASSUMED, single source; method validated on -4/-12) | A19 (user 2026-10-18, group 1 certain): HEXB@HEX 2 -&gt; OMi 2.125 (Items!R1683, M156)</t>
+          <t>ORB_GRVW measured from Brennan 6400-32-20-O STEP (ASSUMED, single source; method validated on -4/-12) | A19 (user 2026-10-18, group 1 certain): HEXB@HEX 2 -&gt; OMi 2.125 (Items!R1683, M156) | 2026-10-20 Air-Way first: HEXB@HEX OMi/Brennan 2.125 -&gt; Air-Way 2</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
